--- a/output/admin-reporting/payments.xlsx
+++ b/output/admin-reporting/payments.xlsx
@@ -2138,7 +2138,7 @@
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
